--- a/Materials/Расписание 2026-2027/Расписание_V34_бланк.xlsx
+++ b/Materials/Расписание 2026-2027/Расписание_V34_бланк.xlsx
@@ -9,10 +9,14 @@
   <sheets>
     <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="1-4 классы" sheetId="1" state="visible" r:id="rId1"/>
     <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="5-11 классы" sheetId="2" state="visible" r:id="rId2"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="ЛУО" sheetId="3" state="visible" r:id="rId3"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="ДО" sheetId="4" state="visible" r:id="rId4"/>
   </sheets>
   <definedNames>
     <definedName name="_xlnm.Print_Titles" localSheetId="0">'1-4 классы'!$1:$5,'1-4 классы'!$A:$B</definedName>
     <definedName name="_xlnm.Print_Titles" localSheetId="1">'5-11 классы'!$1:$5,'5-11 классы'!$A:$B</definedName>
+    <definedName name="_xlnm.Print_Titles" localSheetId="2">'ЛУО'!$1:$8,'ЛУО'!$A:$B</definedName>
+    <definedName name="_xlnm.Print_Titles" localSheetId="3">'ДО'!$1:$8,'ДО'!$A:$B</definedName>
   </definedNames>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
 </workbook>
@@ -121,7 +125,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="11">
+  <cellXfs count="13">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="left" vertical="center" wrapText="1"/>
@@ -149,6 +153,8 @@
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="4" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0" hidden="0"/>
@@ -3024,7 +3030,7 @@
       <c r="G25" s="9" t="inlineStr"/>
       <c r="H25" s="9" t="inlineStr">
         <is>
-          <t>Худ.труд</t>
+          <t>Физкультура</t>
         </is>
       </c>
       <c r="I25" s="9" t="inlineStr">
@@ -3150,7 +3156,7 @@
       <c r="G27" s="9" t="inlineStr"/>
       <c r="H27" s="9" t="inlineStr">
         <is>
-          <t>Физкультура</t>
+          <t>Физика</t>
         </is>
       </c>
       <c r="I27" s="9" t="inlineStr">
@@ -3199,11 +3205,7 @@
       <c r="E28" s="9" t="inlineStr"/>
       <c r="F28" s="9" t="inlineStr"/>
       <c r="G28" s="9" t="inlineStr"/>
-      <c r="H28" s="9" t="inlineStr">
-        <is>
-          <t>Физика</t>
-        </is>
-      </c>
+      <c r="H28" s="9" t="inlineStr"/>
       <c r="I28" s="9" t="inlineStr"/>
       <c r="J28" s="9" t="inlineStr">
         <is>
@@ -3578,7 +3580,7 @@
       </c>
       <c r="K34" s="9" t="inlineStr">
         <is>
-          <t>Геометрия</t>
+          <t>Всем.история</t>
         </is>
       </c>
       <c r="L34" s="9" t="inlineStr">
@@ -3641,7 +3643,7 @@
       </c>
       <c r="K35" s="9" t="inlineStr">
         <is>
-          <t>Всем.история</t>
+          <t>Геометрия</t>
         </is>
       </c>
       <c r="L35" s="9" t="inlineStr">
@@ -3767,7 +3769,7 @@
       </c>
       <c r="H38" s="8" t="inlineStr">
         <is>
-          <t>Физика</t>
+          <t>Худ.труд</t>
         </is>
       </c>
       <c r="I38" s="8" t="inlineStr">
@@ -3782,7 +3784,7 @@
       </c>
       <c r="K38" s="8" t="inlineStr">
         <is>
-          <t>Каз. литература</t>
+          <t>Казахский язык</t>
         </is>
       </c>
       <c r="L38" s="8" t="inlineStr">
@@ -4112,7 +4114,11 @@
         </is>
       </c>
       <c r="G43" s="9" t="inlineStr"/>
-      <c r="H43" s="9" t="inlineStr"/>
+      <c r="H43" s="9" t="inlineStr">
+        <is>
+          <t>Физика</t>
+        </is>
+      </c>
       <c r="I43" s="9" t="inlineStr">
         <is>
           <t>Физкультура</t>
@@ -4218,4 +4224,876 @@
   <pageMargins left="0.3" right="0.3" top="0.4" bottom="0.4" header="0.2" footer="0.2"/>
   <pageSetup orientation="landscape" fitToHeight="0" fitToWidth="1"/>
 </worksheet>
+</file>
+
+<file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <sheetPr>
+    <outlinePr summaryBelow="1" summaryRight="1"/>
+    <pageSetUpPr fitToPage="1"/>
+  </sheetPr>
+  <dimension ref="A1:C38"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <cols>
+    <col width="4" customWidth="1" min="1" max="1"/>
+    <col width="5" customWidth="1" min="2" max="2"/>
+    <col width="15" customWidth="1" min="3" max="3"/>
+  </cols>
+  <sheetData>
+    <row r="1" ht="17" customHeight="1">
+      <c r="A1" s="11" t="inlineStr">
+        <is>
+          <t>«Согласовано»</t>
+        </is>
+      </c>
+      <c r="C1" s="11" t="inlineStr">
+        <is>
+          <t>«Утверждаю»</t>
+        </is>
+      </c>
+    </row>
+    <row r="2" ht="18" customHeight="1">
+      <c r="A2" s="12" t="inlineStr">
+        <is>
+          <t>Председатель родительского комитета:</t>
+        </is>
+      </c>
+      <c r="C2" s="12" t="inlineStr">
+        <is>
+          <t>Директор школы:</t>
+        </is>
+      </c>
+    </row>
+    <row r="3" ht="18" customHeight="1">
+      <c r="A3" s="11" t="inlineStr">
+        <is>
+          <t>Чоп Н.А.</t>
+        </is>
+      </c>
+      <c r="C3" s="11" t="inlineStr">
+        <is>
+          <t>Мельников П.В.</t>
+        </is>
+      </c>
+    </row>
+    <row r="4" ht="6" customHeight="1"/>
+    <row r="5" ht="20" customHeight="1">
+      <c r="A5" s="3" t="inlineStr">
+        <is>
+          <t>Расписание уроков на I полугодие</t>
+        </is>
+      </c>
+    </row>
+    <row r="6" ht="18" customHeight="1">
+      <c r="A6" s="4" t="inlineStr">
+        <is>
+          <t>КГУ «Песчанская СОШ №1» 2026-2027 учебный год (ЛУО)</t>
+        </is>
+      </c>
+    </row>
+    <row r="7" ht="6" customHeight="1"/>
+    <row r="8" ht="30" customHeight="1">
+      <c r="A8" s="5" t="n"/>
+      <c r="B8" s="5" t="n"/>
+      <c r="C8" s="6" t="inlineStr">
+        <is>
+          <t>Власова Анастасия (7А)</t>
+        </is>
+      </c>
+    </row>
+    <row r="9" ht="20" customHeight="1">
+      <c r="A9" s="7" t="inlineStr">
+        <is>
+          <t>Пн</t>
+        </is>
+      </c>
+      <c r="B9" s="8" t="n">
+        <v>1</v>
+      </c>
+      <c r="C9" s="8" t="inlineStr">
+        <is>
+          <t>Алгебра/Геометрия</t>
+        </is>
+      </c>
+    </row>
+    <row r="10" ht="20" customHeight="1">
+      <c r="A10" s="5" t="n"/>
+      <c r="B10" s="9" t="n">
+        <v>2</v>
+      </c>
+      <c r="C10" s="9" t="inlineStr"/>
+    </row>
+    <row r="11" ht="20" customHeight="1">
+      <c r="A11" s="5" t="n"/>
+      <c r="B11" s="9" t="n">
+        <v>3</v>
+      </c>
+      <c r="C11" s="9" t="inlineStr">
+        <is>
+          <t>Русская лит.</t>
+        </is>
+      </c>
+    </row>
+    <row r="12" ht="20" customHeight="1">
+      <c r="A12" s="5" t="n"/>
+      <c r="B12" s="9" t="n">
+        <v>4</v>
+      </c>
+      <c r="C12" s="9" t="inlineStr">
+        <is>
+          <t>Биология</t>
+        </is>
+      </c>
+    </row>
+    <row r="13" ht="20" customHeight="1">
+      <c r="A13" s="5" t="n"/>
+      <c r="B13" s="9" t="n">
+        <v>5</v>
+      </c>
+      <c r="C13" s="9" t="inlineStr"/>
+    </row>
+    <row r="14" ht="20" customHeight="1">
+      <c r="A14" s="10" t="n"/>
+      <c r="B14" s="9" t="n">
+        <v>6</v>
+      </c>
+      <c r="C14" s="9" t="inlineStr">
+        <is>
+          <t>Физкультура</t>
+        </is>
+      </c>
+    </row>
+    <row r="15" ht="20" customHeight="1">
+      <c r="A15" s="7" t="inlineStr">
+        <is>
+          <t>Вт</t>
+        </is>
+      </c>
+      <c r="B15" s="8" t="n">
+        <v>1</v>
+      </c>
+      <c r="C15" s="8" t="inlineStr">
+        <is>
+          <t>География</t>
+        </is>
+      </c>
+    </row>
+    <row r="16" ht="20" customHeight="1">
+      <c r="A16" s="5" t="n"/>
+      <c r="B16" s="9" t="n">
+        <v>2</v>
+      </c>
+      <c r="C16" s="9" t="inlineStr">
+        <is>
+          <t>КиЛ</t>
+        </is>
+      </c>
+    </row>
+    <row r="17" ht="20" customHeight="1">
+      <c r="A17" s="5" t="n"/>
+      <c r="B17" s="9" t="n">
+        <v>3</v>
+      </c>
+      <c r="C17" s="9" t="inlineStr">
+        <is>
+          <t>Русский язык</t>
+        </is>
+      </c>
+    </row>
+    <row r="18" ht="20" customHeight="1">
+      <c r="A18" s="5" t="n"/>
+      <c r="B18" s="9" t="n">
+        <v>4</v>
+      </c>
+      <c r="C18" s="9" t="inlineStr">
+        <is>
+          <t>История Каз.</t>
+        </is>
+      </c>
+    </row>
+    <row r="19" ht="20" customHeight="1">
+      <c r="A19" s="10" t="n"/>
+      <c r="B19" s="9" t="n">
+        <v>5</v>
+      </c>
+      <c r="C19" s="9" t="inlineStr">
+        <is>
+          <t>Алгебра/Геометрия</t>
+        </is>
+      </c>
+    </row>
+    <row r="20" ht="20" customHeight="1">
+      <c r="A20" s="7" t="inlineStr">
+        <is>
+          <t>Ср</t>
+        </is>
+      </c>
+      <c r="B20" s="8" t="n">
+        <v>1</v>
+      </c>
+      <c r="C20" s="8" t="inlineStr">
+        <is>
+          <t>Биология</t>
+        </is>
+      </c>
+    </row>
+    <row r="21" ht="20" customHeight="1">
+      <c r="A21" s="5" t="n"/>
+      <c r="B21" s="9" t="n">
+        <v>2</v>
+      </c>
+      <c r="C21" s="9" t="inlineStr">
+        <is>
+          <t>Русский язык</t>
+        </is>
+      </c>
+    </row>
+    <row r="22" ht="20" customHeight="1">
+      <c r="A22" s="5" t="n"/>
+      <c r="B22" s="9" t="n">
+        <v>3</v>
+      </c>
+      <c r="C22" s="9" t="inlineStr">
+        <is>
+          <t>Алгебра/Геометрия</t>
+        </is>
+      </c>
+    </row>
+    <row r="23" ht="20" customHeight="1">
+      <c r="A23" s="5" t="n"/>
+      <c r="B23" s="9" t="n">
+        <v>4</v>
+      </c>
+      <c r="C23" s="9" t="inlineStr">
+        <is>
+          <t>Физкультура</t>
+        </is>
+      </c>
+    </row>
+    <row r="24" ht="20" customHeight="1">
+      <c r="A24" s="10" t="n"/>
+      <c r="B24" s="9" t="n">
+        <v>5</v>
+      </c>
+      <c r="C24" s="9" t="inlineStr">
+        <is>
+          <t>КиЛ</t>
+        </is>
+      </c>
+    </row>
+    <row r="25" ht="20" customHeight="1">
+      <c r="A25" s="7" t="inlineStr">
+        <is>
+          <t>Чт</t>
+        </is>
+      </c>
+      <c r="B25" s="8" t="n">
+        <v>1</v>
+      </c>
+      <c r="C25" s="8" t="inlineStr">
+        <is>
+          <t>История Каз.</t>
+        </is>
+      </c>
+    </row>
+    <row r="26" ht="20" customHeight="1">
+      <c r="A26" s="5" t="n"/>
+      <c r="B26" s="9" t="n">
+        <v>2</v>
+      </c>
+      <c r="C26" s="9" t="inlineStr"/>
+    </row>
+    <row r="27" ht="20" customHeight="1">
+      <c r="A27" s="5" t="n"/>
+      <c r="B27" s="9" t="n">
+        <v>3</v>
+      </c>
+      <c r="C27" s="9" t="inlineStr">
+        <is>
+          <t>Алгебра/Геометрия</t>
+        </is>
+      </c>
+    </row>
+    <row r="28" ht="20" customHeight="1">
+      <c r="A28" s="5" t="n"/>
+      <c r="B28" s="9" t="n">
+        <v>4</v>
+      </c>
+      <c r="C28" s="9" t="inlineStr"/>
+    </row>
+    <row r="29" ht="20" customHeight="1">
+      <c r="A29" s="5" t="n"/>
+      <c r="B29" s="9" t="n">
+        <v>5</v>
+      </c>
+      <c r="C29" s="9" t="inlineStr">
+        <is>
+          <t>Русский язык</t>
+        </is>
+      </c>
+    </row>
+    <row r="30" ht="20" customHeight="1">
+      <c r="A30" s="5" t="n"/>
+      <c r="B30" s="9" t="n">
+        <v>6</v>
+      </c>
+      <c r="C30" s="9" t="inlineStr">
+        <is>
+          <t>География</t>
+        </is>
+      </c>
+    </row>
+    <row r="31" ht="20" customHeight="1">
+      <c r="A31" s="10" t="n"/>
+      <c r="B31" s="9" t="n">
+        <v>7</v>
+      </c>
+      <c r="C31" s="9" t="inlineStr">
+        <is>
+          <t>Физкультура</t>
+        </is>
+      </c>
+    </row>
+    <row r="32" ht="20" customHeight="1">
+      <c r="A32" s="7" t="inlineStr">
+        <is>
+          <t>Пт</t>
+        </is>
+      </c>
+      <c r="B32" s="8" t="n">
+        <v>1</v>
+      </c>
+      <c r="C32" s="8" t="inlineStr">
+        <is>
+          <t>Худ.труд</t>
+        </is>
+      </c>
+    </row>
+    <row r="33" ht="20" customHeight="1">
+      <c r="A33" s="5" t="n"/>
+      <c r="B33" s="9" t="n">
+        <v>2</v>
+      </c>
+      <c r="C33" s="9" t="inlineStr"/>
+    </row>
+    <row r="34" ht="20" customHeight="1">
+      <c r="A34" s="5" t="n"/>
+      <c r="B34" s="9" t="n">
+        <v>3</v>
+      </c>
+      <c r="C34" s="9" t="inlineStr">
+        <is>
+          <t>Алгебра/Геометрия</t>
+        </is>
+      </c>
+    </row>
+    <row r="35" ht="20" customHeight="1">
+      <c r="A35" s="5" t="n"/>
+      <c r="B35" s="9" t="n">
+        <v>4</v>
+      </c>
+      <c r="C35" s="9" t="inlineStr"/>
+    </row>
+    <row r="36" ht="20" customHeight="1">
+      <c r="A36" s="10" t="n"/>
+      <c r="B36" s="9" t="n">
+        <v>5</v>
+      </c>
+      <c r="C36" s="9" t="inlineStr">
+        <is>
+          <t>Русская лит.</t>
+        </is>
+      </c>
+    </row>
+    <row r="38" ht="22" customHeight="1">
+      <c r="A38" s="1" t="inlineStr">
+        <is>
+          <t>Составила: ЗДУВР Квашнина Е.В.</t>
+        </is>
+      </c>
+    </row>
+  </sheetData>
+  <mergeCells count="8">
+    <mergeCell ref="A9:A14"/>
+    <mergeCell ref="A5:C5"/>
+    <mergeCell ref="A15:A19"/>
+    <mergeCell ref="A25:A31"/>
+    <mergeCell ref="A6:C6"/>
+    <mergeCell ref="A20:A24"/>
+    <mergeCell ref="A32:A36"/>
+    <mergeCell ref="A38:C38"/>
+  </mergeCells>
+  <pageMargins left="0.3" right="0.3" top="0.4" bottom="0.4" header="0.2" footer="0.2"/>
+  <pageSetup orientation="landscape" fitToHeight="0" fitToWidth="1"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <sheetPr>
+    <outlinePr summaryBelow="1" summaryRight="1"/>
+    <pageSetUpPr fitToPage="1"/>
+  </sheetPr>
+  <dimension ref="A1:F31"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <cols>
+    <col width="4" customWidth="1" min="1" max="1"/>
+    <col width="5" customWidth="1" min="2" max="2"/>
+    <col width="15" customWidth="1" min="3" max="3"/>
+    <col width="15" customWidth="1" min="4" max="4"/>
+    <col width="15" customWidth="1" min="5" max="5"/>
+    <col width="15" customWidth="1" min="6" max="6"/>
+  </cols>
+  <sheetData>
+    <row r="1" ht="17" customHeight="1">
+      <c r="A1" s="11" t="inlineStr">
+        <is>
+          <t>«Согласовано»</t>
+        </is>
+      </c>
+      <c r="F1" s="11" t="inlineStr">
+        <is>
+          <t>«Утверждаю»</t>
+        </is>
+      </c>
+    </row>
+    <row r="2" ht="18" customHeight="1">
+      <c r="A2" s="12" t="inlineStr">
+        <is>
+          <t>Председатель родительского комитета:</t>
+        </is>
+      </c>
+      <c r="F2" s="12" t="inlineStr">
+        <is>
+          <t>Директор школы:</t>
+        </is>
+      </c>
+    </row>
+    <row r="3" ht="18" customHeight="1">
+      <c r="A3" s="11" t="inlineStr">
+        <is>
+          <t>Чоп Н.А.</t>
+        </is>
+      </c>
+      <c r="F3" s="11" t="inlineStr">
+        <is>
+          <t>Мельников П.В.</t>
+        </is>
+      </c>
+    </row>
+    <row r="4" ht="6" customHeight="1"/>
+    <row r="5" ht="20" customHeight="1">
+      <c r="A5" s="3" t="inlineStr">
+        <is>
+          <t>Расписание уроков на I полугодие</t>
+        </is>
+      </c>
+    </row>
+    <row r="6" ht="18" customHeight="1">
+      <c r="A6" s="4" t="inlineStr">
+        <is>
+          <t>КГУ «Песчанская СОШ №1» 2026-2027 учебный год (ДО)</t>
+        </is>
+      </c>
+    </row>
+    <row r="7" ht="6" customHeight="1"/>
+    <row r="8" ht="30" customHeight="1">
+      <c r="A8" s="5" t="n"/>
+      <c r="B8" s="5" t="n"/>
+      <c r="C8" s="6" t="inlineStr">
+        <is>
+          <t>Тургумбаева Айсана (8Б)</t>
+        </is>
+      </c>
+      <c r="D8" s="6" t="inlineStr">
+        <is>
+          <t>Желнин Матвей (7А)</t>
+        </is>
+      </c>
+      <c r="E8" s="6" t="inlineStr">
+        <is>
+          <t>Романов Никита (9Б)</t>
+        </is>
+      </c>
+      <c r="F8" s="6" t="inlineStr">
+        <is>
+          <t>Галле Оливия (1Б)</t>
+        </is>
+      </c>
+    </row>
+    <row r="9" ht="20" customHeight="1">
+      <c r="A9" s="7" t="inlineStr">
+        <is>
+          <t>Пн</t>
+        </is>
+      </c>
+      <c r="B9" s="8" t="n">
+        <v>1</v>
+      </c>
+      <c r="C9" s="8" t="inlineStr"/>
+      <c r="D9" s="8" t="inlineStr">
+        <is>
+          <t>Разв. речи и комм.</t>
+        </is>
+      </c>
+      <c r="E9" s="8" t="inlineStr"/>
+      <c r="F9" s="8" t="inlineStr"/>
+    </row>
+    <row r="10" ht="20" customHeight="1">
+      <c r="A10" s="5" t="n"/>
+      <c r="B10" s="9" t="n">
+        <v>2</v>
+      </c>
+      <c r="C10" s="9" t="inlineStr">
+        <is>
+          <t>Русский язык</t>
+        </is>
+      </c>
+      <c r="D10" s="9" t="inlineStr">
+        <is>
+          <t>Хоз. труд</t>
+        </is>
+      </c>
+      <c r="E10" s="9" t="inlineStr"/>
+      <c r="F10" s="9" t="inlineStr"/>
+    </row>
+    <row r="11" ht="20" customHeight="1">
+      <c r="A11" s="5" t="n"/>
+      <c r="B11" s="9" t="n">
+        <v>3</v>
+      </c>
+      <c r="C11" s="9" t="inlineStr">
+        <is>
+          <t>Математика</t>
+        </is>
+      </c>
+      <c r="D11" s="9" t="inlineStr"/>
+      <c r="E11" s="9" t="inlineStr">
+        <is>
+          <t>Разв. речи и комм.</t>
+        </is>
+      </c>
+      <c r="F11" s="9" t="inlineStr"/>
+    </row>
+    <row r="12" ht="20" customHeight="1">
+      <c r="A12" s="10" t="n"/>
+      <c r="B12" s="9" t="n">
+        <v>4</v>
+      </c>
+      <c r="C12" s="9" t="inlineStr"/>
+      <c r="D12" s="9" t="inlineStr"/>
+      <c r="E12" s="9" t="inlineStr">
+        <is>
+          <t>Человек и мир</t>
+        </is>
+      </c>
+      <c r="F12" s="9" t="inlineStr"/>
+    </row>
+    <row r="13" ht="20" customHeight="1">
+      <c r="A13" s="7" t="inlineStr">
+        <is>
+          <t>Вт</t>
+        </is>
+      </c>
+      <c r="B13" s="8" t="n">
+        <v>1</v>
+      </c>
+      <c r="C13" s="8" t="inlineStr"/>
+      <c r="D13" s="8" t="inlineStr">
+        <is>
+          <t>ИЗО</t>
+        </is>
+      </c>
+      <c r="E13" s="8" t="inlineStr"/>
+      <c r="F13" s="8" t="inlineStr"/>
+    </row>
+    <row r="14" ht="20" customHeight="1">
+      <c r="A14" s="5" t="n"/>
+      <c r="B14" s="9" t="n">
+        <v>2</v>
+      </c>
+      <c r="C14" s="9" t="inlineStr">
+        <is>
+          <t>Математика</t>
+        </is>
+      </c>
+      <c r="D14" s="9" t="inlineStr">
+        <is>
+          <t>Человек и мир</t>
+        </is>
+      </c>
+      <c r="E14" s="9" t="inlineStr"/>
+      <c r="F14" s="9" t="inlineStr"/>
+    </row>
+    <row r="15" ht="20" customHeight="1">
+      <c r="A15" s="5" t="n"/>
+      <c r="B15" s="9" t="n">
+        <v>3</v>
+      </c>
+      <c r="C15" s="9" t="inlineStr">
+        <is>
+          <t>СБО / История Каз.</t>
+        </is>
+      </c>
+      <c r="D15" s="9" t="inlineStr"/>
+      <c r="E15" s="9" t="inlineStr">
+        <is>
+          <t>Счет</t>
+        </is>
+      </c>
+      <c r="F15" s="9" t="inlineStr"/>
+    </row>
+    <row r="16" ht="20" customHeight="1">
+      <c r="A16" s="5" t="n"/>
+      <c r="B16" s="9" t="n">
+        <v>4</v>
+      </c>
+      <c r="C16" s="9" t="inlineStr"/>
+      <c r="D16" s="9" t="inlineStr"/>
+      <c r="E16" s="9" t="inlineStr">
+        <is>
+          <t>Познав. развитие</t>
+        </is>
+      </c>
+      <c r="F16" s="9" t="inlineStr"/>
+    </row>
+    <row r="17" ht="20" customHeight="1">
+      <c r="A17" s="10" t="n"/>
+      <c r="B17" s="9" t="n">
+        <v>5</v>
+      </c>
+      <c r="C17" s="9" t="inlineStr"/>
+      <c r="D17" s="9" t="inlineStr"/>
+      <c r="E17" s="9" t="inlineStr">
+        <is>
+          <t>СБО</t>
+        </is>
+      </c>
+      <c r="F17" s="9" t="inlineStr"/>
+    </row>
+    <row r="18" ht="20" customHeight="1">
+      <c r="A18" s="7" t="inlineStr">
+        <is>
+          <t>Ср</t>
+        </is>
+      </c>
+      <c r="B18" s="8" t="n">
+        <v>1</v>
+      </c>
+      <c r="C18" s="8" t="inlineStr"/>
+      <c r="D18" s="8" t="inlineStr">
+        <is>
+          <t>Познав. развитие</t>
+        </is>
+      </c>
+      <c r="E18" s="8" t="inlineStr"/>
+      <c r="F18" s="8" t="inlineStr"/>
+    </row>
+    <row r="19" ht="20" customHeight="1">
+      <c r="A19" s="5" t="n"/>
+      <c r="B19" s="9" t="n">
+        <v>2</v>
+      </c>
+      <c r="C19" s="9" t="inlineStr">
+        <is>
+          <t>Лит. чтение</t>
+        </is>
+      </c>
+      <c r="D19" s="9" t="inlineStr">
+        <is>
+          <t>Счет</t>
+        </is>
+      </c>
+      <c r="E19" s="9" t="inlineStr"/>
+      <c r="F19" s="9" t="inlineStr">
+        <is>
+          <t>ИЗО</t>
+        </is>
+      </c>
+    </row>
+    <row r="20" ht="20" customHeight="1">
+      <c r="A20" s="5" t="n"/>
+      <c r="B20" s="9" t="n">
+        <v>3</v>
+      </c>
+      <c r="C20" s="9" t="inlineStr">
+        <is>
+          <t>Естествознание / География</t>
+        </is>
+      </c>
+      <c r="D20" s="9" t="inlineStr"/>
+      <c r="E20" s="9" t="inlineStr">
+        <is>
+          <t>Разв. речи и комм.</t>
+        </is>
+      </c>
+      <c r="F20" s="9" t="inlineStr"/>
+    </row>
+    <row r="21" ht="20" customHeight="1">
+      <c r="A21" s="5" t="n"/>
+      <c r="B21" s="9" t="n">
+        <v>4</v>
+      </c>
+      <c r="C21" s="9" t="inlineStr"/>
+      <c r="D21" s="9" t="inlineStr"/>
+      <c r="E21" s="9" t="inlineStr">
+        <is>
+          <t>Счет</t>
+        </is>
+      </c>
+      <c r="F21" s="9" t="inlineStr"/>
+    </row>
+    <row r="22" ht="20" customHeight="1">
+      <c r="A22" s="10" t="n"/>
+      <c r="B22" s="9" t="n">
+        <v>5</v>
+      </c>
+      <c r="C22" s="9" t="inlineStr"/>
+      <c r="D22" s="9" t="inlineStr"/>
+      <c r="E22" s="9" t="inlineStr">
+        <is>
+          <t>Человек и мир</t>
+        </is>
+      </c>
+      <c r="F22" s="9" t="inlineStr"/>
+    </row>
+    <row r="23" ht="20" customHeight="1">
+      <c r="A23" s="7" t="inlineStr">
+        <is>
+          <t>Чт</t>
+        </is>
+      </c>
+      <c r="B23" s="8" t="n">
+        <v>1</v>
+      </c>
+      <c r="C23" s="8" t="inlineStr"/>
+      <c r="D23" s="8" t="inlineStr">
+        <is>
+          <t>СБО</t>
+        </is>
+      </c>
+      <c r="E23" s="8" t="inlineStr"/>
+      <c r="F23" s="8" t="inlineStr"/>
+    </row>
+    <row r="24" ht="20" customHeight="1">
+      <c r="A24" s="5" t="n"/>
+      <c r="B24" s="9" t="n">
+        <v>2</v>
+      </c>
+      <c r="C24" s="9" t="inlineStr">
+        <is>
+          <t>Казахский язык</t>
+        </is>
+      </c>
+      <c r="D24" s="9" t="inlineStr">
+        <is>
+          <t>Разв. речи и комм.</t>
+        </is>
+      </c>
+      <c r="E24" s="9" t="inlineStr"/>
+      <c r="F24" s="9" t="inlineStr"/>
+    </row>
+    <row r="25" ht="20" customHeight="1">
+      <c r="A25" s="5" t="n"/>
+      <c r="B25" s="9" t="n">
+        <v>3</v>
+      </c>
+      <c r="C25" s="9" t="inlineStr">
+        <is>
+          <t>Инд.-развив. занятия</t>
+        </is>
+      </c>
+      <c r="D25" s="9" t="inlineStr"/>
+      <c r="E25" s="9" t="inlineStr">
+        <is>
+          <t>ИЗО</t>
+        </is>
+      </c>
+      <c r="F25" s="9" t="inlineStr"/>
+    </row>
+    <row r="26" ht="20" customHeight="1">
+      <c r="A26" s="10" t="n"/>
+      <c r="B26" s="9" t="n">
+        <v>4</v>
+      </c>
+      <c r="C26" s="9" t="inlineStr"/>
+      <c r="D26" s="9" t="inlineStr"/>
+      <c r="E26" s="9" t="inlineStr">
+        <is>
+          <t>Хоз. труд</t>
+        </is>
+      </c>
+      <c r="F26" s="9" t="inlineStr"/>
+    </row>
+    <row r="27" ht="20" customHeight="1">
+      <c r="A27" s="7" t="inlineStr">
+        <is>
+          <t>Пт</t>
+        </is>
+      </c>
+      <c r="B27" s="8" t="n">
+        <v>1</v>
+      </c>
+      <c r="C27" s="8" t="inlineStr"/>
+      <c r="D27" s="8" t="inlineStr">
+        <is>
+          <t>Счет</t>
+        </is>
+      </c>
+      <c r="E27" s="8" t="inlineStr"/>
+      <c r="F27" s="8" t="inlineStr"/>
+    </row>
+    <row r="28" ht="20" customHeight="1">
+      <c r="A28" s="5" t="n"/>
+      <c r="B28" s="9" t="n">
+        <v>2</v>
+      </c>
+      <c r="C28" s="9" t="inlineStr">
+        <is>
+          <t>Русский язык</t>
+        </is>
+      </c>
+      <c r="D28" s="9" t="inlineStr">
+        <is>
+          <t>Человек и мир</t>
+        </is>
+      </c>
+      <c r="E28" s="9" t="inlineStr"/>
+      <c r="F28" s="9" t="inlineStr"/>
+    </row>
+    <row r="29" ht="20" customHeight="1">
+      <c r="A29" s="10" t="n"/>
+      <c r="B29" s="9" t="n">
+        <v>3</v>
+      </c>
+      <c r="C29" s="9" t="inlineStr">
+        <is>
+          <t>Инд.-развив. занятия</t>
+        </is>
+      </c>
+      <c r="D29" s="9" t="inlineStr"/>
+      <c r="E29" s="9" t="inlineStr"/>
+      <c r="F29" s="9" t="inlineStr"/>
+    </row>
+    <row r="31" ht="22" customHeight="1">
+      <c r="A31" s="1" t="inlineStr">
+        <is>
+          <t>Составила: ЗДУВР Квашнина Е.В.</t>
+        </is>
+      </c>
+    </row>
+  </sheetData>
+  <mergeCells count="8">
+    <mergeCell ref="A18:A22"/>
+    <mergeCell ref="A23:A26"/>
+    <mergeCell ref="A9:A12"/>
+    <mergeCell ref="A5:F5"/>
+    <mergeCell ref="A31:F31"/>
+    <mergeCell ref="A6:F6"/>
+    <mergeCell ref="A13:A17"/>
+    <mergeCell ref="A27:A29"/>
+  </mergeCells>
+  <pageMargins left="0.3" right="0.3" top="0.4" bottom="0.4" header="0.2" footer="0.2"/>
+  <pageSetup orientation="landscape" fitToHeight="0" fitToWidth="1"/>
+</worksheet>
 </file>